--- a/artfynd/A 13933-2022 artfynd.xlsx
+++ b/artfynd/A 13933-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13933-2022 artfynd.xlsx
+++ b/artfynd/A 13933-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2623260</v>
+        <v>102365</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R2" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,24 +743,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>110931311 / NEOT NID / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / BUXB VIR / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +765,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Barrnaturskog /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Låga av gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,12 +794,7 @@
         <v>398018</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R3" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +859,9 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-12-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -932,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102365</v>
+        <v>784654</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R4" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,24 +975,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>110931311 / BUXB VIR / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / RHYT SUB / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,11 +997,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrnaturskog /</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Låga av gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5009490</v>
+        <v>2623260</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R5" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1136,24 +1086,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>110931311 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / NEOT NID / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>784654</v>
+        <v>4042610</v>
       </c>
       <c r="B6" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1229,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R6" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1262,24 +1197,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>110931311 / RHYT SUB / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / MONE UNI / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4042610</v>
+        <v>4798361</v>
       </c>
       <c r="B7" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1355,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R7" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1388,24 +1308,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>110931311 / MONE UNI / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / DAPH MEZ / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,15 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4798361</v>
+        <v>5009490</v>
       </c>
       <c r="B8" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702766.4340045939</v>
+        <v>702766</v>
       </c>
       <c r="R8" t="n">
-        <v>6616159.460824305</v>
+        <v>6616159</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1514,24 +1419,14 @@
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2002-12-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>110931311 / DAPH MEZ / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>110931311 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13933-2022 artfynd.xlsx
+++ b/artfynd/A 13933-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/398018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/784654</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2623260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4042610</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4798361</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,8 +1494,22 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5009490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>